--- a/dollarexpress/resources/sample/dollarexpress/dollarExpressGolbal.xlsx
+++ b/dollarexpress/resources/sample/dollarexpress/dollarExpressGolbal.xlsx
@@ -1,39 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\dollarexpress\resources\sample\dollarexpress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81B93AD-8BA3-434E-A1FD-2032B6367513}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992EA05C-C380-4D20-953D-FBEABB096F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DollarExpressGolbalConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{25DCAC83-46E9-434B-9BB7-95CAAFF7E99A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1:绿火车
+2：蓝火车
+3：紫火车
+4：红火车</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>sid</t>
-  </si>
-  <si>
-    <t>免费玩法-触发黄金火车至少需要免费图标数量</t>
   </si>
   <si>
     <t>押注进入水池万分比</t>
@@ -83,12 +109,55 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>免费玩法-触发黄金火车至少需要免费图标数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资触发条件（美元出现X次后触发）</t>
+  </si>
+  <si>
+    <t>投资模式区域</t>
+  </si>
+  <si>
+    <t>1：2：3:4:5|6:7:8:9:10:11|</t>
+  </si>
+  <si>
+    <t>免费模式-拉火车模式中各个颜色火车出现概率/万分比</t>
+  </si>
+  <si>
+    <t>1:10000|2:5000|3:2000|4:1000</t>
+  </si>
+  <si>
+    <t>初始化格子展示</t>
+  </si>
+  <si>
+    <t>1:1:1:1|2:2:2:2|3:3:3:3|4:4:4:4|5:5:5:5</t>
+  </si>
+  <si>
+    <t>金火车美元出现数量和权重</t>
+  </si>
+  <si>
+    <t>3:900|4:1100|5:2000|6:4000|7:2000</t>
+  </si>
+  <si>
+    <t>数字值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +186,19 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,17 +238,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -175,7 +257,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -451,91 +539,171 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="41.125" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="41.125" customWidth="1"/>
+    <col min="4" max="4" width="42.375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>9600</v>
+      </c>
+      <c r="D6">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="5">
-        <v>9600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>5</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>150</v>
+      </c>
+      <c r="D9">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>